--- a/InputFiles/ICDC/TC02_Canine_StudyCOTC022-StudyType_Breed_ResponseToTreatment_NeuteredStatus.xlsx
+++ b/InputFiles/ICDC/TC02_Canine_StudyCOTC022-StudyType_Breed_ResponseToTreatment_NeuteredStatus.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\epishinavv\git\Commons_Automation\InputFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\epishinavv\git\Commons_Automation\InputFiles\ICDC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBBAAE2E-6C1A-47B5-B077-BED005941430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{433D8D59-BA9B-4DCB-AD21-7F543F5B3BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{8362173B-D28C-47E7-8626-98E16101E601}"/>
   </bookViews>
@@ -104,32 +104,40 @@
 limit 100</t>
   </si>
   <si>
-    <t>MATCH (s:study)&lt;-[*]-(c:case)&lt;--(demo:demographic), (samp:sample)--&gt;(c)&lt;--(diag:diagnosis) 
-MATCH (r:registration)--&gt;(c)
+    <t>MATCH (f:file)--&gt;(s:study)
+MATCH (s)&lt;--(c:case)&lt;--(diag:diagnosis)
+MATCH (c)&lt;--(demo:demographic)
 WHERE s.clinical_study_designation IN ['COTC022'] and s.clinical_study_type IN ['Clinical Trial'] and demo.breed in ['Great Pyrenees'] and diag.best_response in ['Progressive Disease'] and demo.neutered_indicator in ['No']
-WITH DISTINCT samp AS samp, c, demo, diag
-RETURN  coalesce(samp.sample_id, '') AS `Sample ID`, 
-        coalesce(c.case_id, '') AS `Case ID`, 
-        coalesce(demo.breed,'') AS Breed,
-        coalesce(diag.disease_term,'') AS Diagnosis, 
-        coalesce(samp.sample_site, '') AS `Sample Site`,
-        coalesce(samp.summarized_sample_type, '') AS `Sample Type`,
-        coalesce(samp.specific_sample_pathology, '') AS `Pathology/Morphology`,
-        coalesce(samp.tumor_grade, '') AS `Tumor Grade`,
-        coalesce(samp.sample_chronology, '') AS `Sample Chronology`,
-        coalesce(samp.percentage_tumor, '') AS `Percentage Tumor`,
-        coalesce(samp.necropsy_sample, '') AS `Necropsy Sample`,
-        coalesce(samp.sample_preservation, '') AS `Sample Preservation`
-order by samp.sample_id asc
-limit 100</t>
+WITH
+        DISTINCT f, c, demo, diag, s,
+        ['Bytes', 'KB', 'MB', 'GB', 'TB'] AS units,
+        toInteger(floor(log(f.file_size)/log(1024))) as i,
+        2 as precision
+WITH
+        f, c, demo, diag, s,
+        f.file_size /(1024^i) AS value, 10^precision AS factor,
+        units[i] as unit
+        WITH
+        f,  c, demo, diag, s, unit,
+        round(factor * value)/factor AS size
+RETURN DISTINCT
+  coalesce(f.file_name, '') AS `File Name`,
+  coalesce(f.file_type, '') AS `File Type`,
+  coalesce("study", '') AS `Association`,
+  coalesce(f.file_description, '') AS `Description`,
+  coalesce(f.file_format, '') AS  Format,
+  CASE size % 1 WHEN 0 THEN apoc.convert.toInteger(size)+' ' +unit ELSE size+' ' +unit END AS Size,
+  coalesce(s.clinical_study_designation,'') AS `Study Code`
+  order by 'File Name' asc
+  limit 100</t>
   </si>
   <si>
     <t>MATCH (f:file)--&gt;(parent)
-WITH DISTINCT f, parent
 MATCH (f)-[*]-&gt;(c:case)&lt;--(demo:demographic)
-MATCH (s:study)&lt;-[*]-(c)&lt;--(diag:diagnosis)
-MATCH (r:registration)--&gt;(c)
-WHERE s.clinical_study_designation IN ['COTC022'] and s.clinical_study_type IN ['Clinical Trial'] and demo.breed in ['Great Pyrenees'] and diag.best_response in ['Progressive Disease'] and demo.neutered_indicator in ['No']
+MATCH (diag:diagnosis)--&gt;(c)
+WHERE demo.breed IN ['Great Pyrenees'] and demo.neutered_indicator in ['No']
+MATCH (s:study)&lt;--(c)
+WHERE s.clinical_study_designation IN ['COTC022'] and s.clinical_study_type IN ['Clinical Trial'] and diag.best_response in ['Progressive Disease']
 OPTIONAL MATCH (f)-[*]-&gt;(samp:sample)
 WITH
         DISTINCT f, parent, c, demo, diag, s, samp,
@@ -159,32 +167,23 @@
         limit 100</t>
   </si>
   <si>
-    <t>MATCH (f:file)--&gt;(s:study)
-MATCH (s)&lt;--(c:case)&lt;--(diag:diagnosis)
-MATCH (c)&lt;--(demo:demographic)
+    <t>MATCH (s:study)&lt;-[*]-(c:case)&lt;--(demo:demographic), (samp:sample)--&gt;(c)&lt;--(diag:diagnosis) 
 WHERE s.clinical_study_designation IN ['COTC022'] and s.clinical_study_type IN ['Clinical Trial'] and demo.breed in ['Great Pyrenees'] and diag.best_response in ['Progressive Disease'] and demo.neutered_indicator in ['No']
-WITH
-        DISTINCT f, c, demo, diag, s,
-        ['Bytes', 'KB', 'MB', 'GB', 'TB'] AS units,
-        toInteger(floor(log(f.file_size)/log(1024))) as i,
-        2 as precision
-WITH
-        f, c, demo, diag, s,
-        f.file_size /(1024^i) AS value, 10^precision AS factor,
-        units[i] as unit
-        WITH
-        f,  c, demo, diag, s, unit,
-        round(factor * value)/factor AS size
-RETURN DISTINCT
-  coalesce(f.file_name, '') AS `File Name`,
-  coalesce(f.file_type, '') AS `File Type`,
-  coalesce("study", '') AS `Association`,
-  coalesce(f.file_description, '') AS `Description`,
-  coalesce(f.file_format, '') AS  Format,
-  CASE size % 1 WHEN 0 THEN apoc.convert.toInteger(size)+' ' +unit ELSE size+' ' +unit END AS Size,
-  coalesce(s.clinical_study_designation,'') AS `Study Code`
-  order by 'File Name' asc
-  limit 100</t>
+WITH DISTINCT samp AS samp, c, demo, diag
+RETURN  coalesce(samp.sample_id, '') AS `Sample ID`, 
+        coalesce(c.case_id, '') AS `Case ID`, 
+        coalesce(demo.breed,'') AS Breed,
+        coalesce(diag.disease_term,'') AS Diagnosis, 
+        coalesce(samp.sample_site, '') AS `Sample Site`,
+        coalesce(samp.summarized_sample_type, '') AS `Sample Type`,
+        coalesce(samp.specific_sample_pathology, '') AS `Pathology/Morphology`,
+        coalesce(samp.tumor_grade, '') AS `Tumor Grade`,
+        coalesce(samp.sample_chronology, '') AS `Sample Chronology`,
+        coalesce(samp.percentage_tumor, '') AS `Percentage Tumor`,
+        coalesce(samp.necropsy_sample, '') AS `Necropsy Sample`,
+        coalesce(samp.sample_preservation, '') AS `Sample Preservation`
+order by samp.sample_id asc
+limit 100</t>
   </si>
 </sst>
 </file>
@@ -266,9 +265,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -306,7 +305,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -412,7 +411,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -554,7 +553,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -609,12 +608,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="351.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" ht="333" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>11</v>
@@ -648,7 +647,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>11</v>
